--- a/BARCODE STATUS.xlsx
+++ b/BARCODE STATUS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyDesktop\PO_PENDING_DASHBOARD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6499D539-48F8-432D-9F64-69451D86CF2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DFC1124-706E-40FD-AD87-81D2CA4CEEDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-107" yWindow="-107" windowWidth="20847" windowHeight="11111" xr2:uid="{0D10C1D6-A153-47F5-8D6D-C632DA29E1C7}"/>
   </bookViews>
@@ -4550,9 +4550,6 @@
     <t>New</t>
   </si>
   <si>
-    <t>NEW BARCODE</t>
-  </si>
-  <si>
     <t>CT474223</t>
   </si>
   <si>
@@ -5973,6 +5970,9 @@
   </si>
   <si>
     <t>CT472994</t>
+  </si>
+  <si>
+    <t>NEW_BAR</t>
   </si>
 </sst>
 </file>
@@ -6346,13 +6346,13 @@
   <dimension ref="A1:B1972"/>
   <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1504</v>
+        <v>1978</v>
       </c>
       <c r="B1" t="s">
         <v>1497</v>
@@ -6392,7 +6392,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="B6" t="s">
         <v>1498</v>
@@ -6432,7 +6432,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="B11" t="s">
         <v>1498</v>
@@ -6512,7 +6512,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="B21" t="s">
         <v>1498</v>
@@ -6568,7 +6568,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="B28" t="s">
         <v>1498</v>
@@ -6648,7 +6648,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="B38" t="s">
         <v>1498</v>
@@ -6912,7 +6912,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="B71" t="s">
         <v>1499</v>
@@ -6952,7 +6952,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="B76" t="s">
         <v>1499</v>
@@ -7008,7 +7008,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="B83" t="s">
         <v>1499</v>
@@ -7144,7 +7144,7 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="B100" t="s">
         <v>1499</v>
@@ -7464,7 +7464,7 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="B140" t="s">
         <v>1499</v>
@@ -7496,7 +7496,7 @@
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="B144" t="s">
         <v>1499</v>
@@ -7520,7 +7520,7 @@
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="B147" t="s">
         <v>1499</v>
@@ -7536,7 +7536,7 @@
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="B149" t="s">
         <v>1499</v>
@@ -7680,7 +7680,7 @@
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="B167" t="s">
         <v>1499</v>
@@ -7744,7 +7744,7 @@
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="B175" t="s">
         <v>1499</v>
@@ -7752,7 +7752,7 @@
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="B176" t="s">
         <v>1499</v>
@@ -7824,7 +7824,7 @@
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="B185" t="s">
         <v>1499</v>
@@ -7976,7 +7976,7 @@
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="B204" t="s">
         <v>1499</v>
@@ -8000,7 +8000,7 @@
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="B207" t="s">
         <v>1499</v>
@@ -8056,7 +8056,7 @@
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="B214" t="s">
         <v>1499</v>
@@ -8176,7 +8176,7 @@
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="B229" t="s">
         <v>1499</v>
@@ -8248,7 +8248,7 @@
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B238" t="s">
         <v>1500</v>
@@ -8312,7 +8312,7 @@
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B246" t="s">
         <v>1500</v>
@@ -8408,7 +8408,7 @@
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="B258" t="s">
         <v>1500</v>
@@ -8432,7 +8432,7 @@
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B261" t="s">
         <v>1500</v>
@@ -8544,7 +8544,7 @@
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="B275" t="s">
         <v>1500</v>
@@ -8744,7 +8744,7 @@
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B300" t="s">
         <v>1500</v>
@@ -8896,7 +8896,7 @@
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B319" t="s">
         <v>1500</v>
@@ -8944,7 +8944,7 @@
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="B325" t="s">
         <v>1500</v>
@@ -8952,7 +8952,7 @@
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="B326" t="s">
         <v>1500</v>
@@ -9152,7 +9152,7 @@
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="B351" t="s">
         <v>1500</v>
@@ -9240,7 +9240,7 @@
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="B362" t="s">
         <v>1500</v>
@@ -9296,7 +9296,7 @@
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="B369" t="s">
         <v>1500</v>
@@ -9312,7 +9312,7 @@
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="B371" t="s">
         <v>1500</v>
@@ -9400,7 +9400,7 @@
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="B382" t="s">
         <v>1500</v>
@@ -9464,7 +9464,7 @@
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="B390" t="s">
         <v>1500</v>
@@ -9600,7 +9600,7 @@
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="B407" t="s">
         <v>1500</v>
@@ -9608,7 +9608,7 @@
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="B408" t="s">
         <v>1500</v>
@@ -9792,7 +9792,7 @@
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="B431" t="s">
         <v>1500</v>
@@ -9800,7 +9800,7 @@
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="B432" t="s">
         <v>1500</v>
@@ -9992,7 +9992,7 @@
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="B456" t="s">
         <v>1500</v>
@@ -10032,7 +10032,7 @@
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="B461" t="s">
         <v>1500</v>
@@ -10104,7 +10104,7 @@
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="B470" t="s">
         <v>1500</v>
@@ -10288,7 +10288,7 @@
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="B493" t="s">
         <v>1500</v>
@@ -10472,7 +10472,7 @@
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="B516" t="s">
         <v>1500</v>
@@ -10528,7 +10528,7 @@
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="B523" t="s">
         <v>1500</v>
@@ -10552,7 +10552,7 @@
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="B526" t="s">
         <v>1500</v>
@@ -10576,7 +10576,7 @@
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="B529" t="s">
         <v>1500</v>
@@ -10600,7 +10600,7 @@
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="B532" t="s">
         <v>1500</v>
@@ -10608,7 +10608,7 @@
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="B533" t="s">
         <v>1500</v>
@@ -10736,7 +10736,7 @@
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="B549" t="s">
         <v>1500</v>
@@ -10744,7 +10744,7 @@
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="B550" t="s">
         <v>1500</v>
@@ -10880,7 +10880,7 @@
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="B567" t="s">
         <v>1500</v>
@@ -10984,7 +10984,7 @@
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="B580" t="s">
         <v>1500</v>
@@ -11024,7 +11024,7 @@
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="B585" t="s">
         <v>1500</v>
@@ -11168,7 +11168,7 @@
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="B603" t="s">
         <v>1500</v>
@@ -11400,7 +11400,7 @@
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="B632" t="s">
         <v>1500</v>
@@ -11416,7 +11416,7 @@
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="B634" t="s">
         <v>1500</v>
@@ -11472,7 +11472,7 @@
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="B641" t="s">
         <v>1500</v>
@@ -11600,7 +11600,7 @@
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="B657" t="s">
         <v>1500</v>
@@ -11672,7 +11672,7 @@
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="B666" t="s">
         <v>1500</v>
@@ -11728,7 +11728,7 @@
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="B673" t="s">
         <v>1500</v>
@@ -11752,7 +11752,7 @@
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="B676" t="s">
         <v>1500</v>
@@ -11832,7 +11832,7 @@
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="B686" t="s">
         <v>1500</v>
@@ -11896,7 +11896,7 @@
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="B694" t="s">
         <v>1500</v>
@@ -12096,7 +12096,7 @@
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="B719" t="s">
         <v>1500</v>
@@ -12112,7 +12112,7 @@
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="B721" t="s">
         <v>1500</v>
@@ -12136,7 +12136,7 @@
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="B724" t="s">
         <v>1500</v>
@@ -12200,7 +12200,7 @@
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="B732" t="s">
         <v>1500</v>
@@ -12288,7 +12288,7 @@
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="B743" t="s">
         <v>1500</v>
@@ -12296,7 +12296,7 @@
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="B744" t="s">
         <v>1500</v>
@@ -12336,7 +12336,7 @@
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="B749" t="s">
         <v>1500</v>
@@ -12360,7 +12360,7 @@
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="B752" t="s">
         <v>1500</v>
@@ -12440,7 +12440,7 @@
     </row>
     <row r="762" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="B762" t="s">
         <v>1500</v>
@@ -12576,7 +12576,7 @@
     </row>
     <row r="779" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="B779" t="s">
         <v>1500</v>
@@ -12712,7 +12712,7 @@
     </row>
     <row r="796" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="B796" t="s">
         <v>1500</v>
@@ -12768,7 +12768,7 @@
     </row>
     <row r="803" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="B803" t="s">
         <v>1500</v>
@@ -12776,7 +12776,7 @@
     </row>
     <row r="804" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="B804" t="s">
         <v>1500</v>
@@ -12824,7 +12824,7 @@
     </row>
     <row r="810" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="B810" t="s">
         <v>1500</v>
@@ -12912,7 +12912,7 @@
     </row>
     <row r="821" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="B821" t="s">
         <v>1500</v>
@@ -12984,7 +12984,7 @@
     </row>
     <row r="830" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="B830" t="s">
         <v>1500</v>
@@ -13016,7 +13016,7 @@
     </row>
     <row r="834" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="B834" t="s">
         <v>1500</v>
@@ -13032,7 +13032,7 @@
     </row>
     <row r="836" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="B836" t="s">
         <v>1500</v>
@@ -13064,7 +13064,7 @@
     </row>
     <row r="840" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B840" t="s">
         <v>1500</v>
@@ -13136,7 +13136,7 @@
     </row>
     <row r="849" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B849" t="s">
         <v>1500</v>
@@ -13184,7 +13184,7 @@
     </row>
     <row r="855" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="B855" t="s">
         <v>1500</v>
@@ -13304,7 +13304,7 @@
     </row>
     <row r="870" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="B870" t="s">
         <v>1500</v>
@@ -13344,7 +13344,7 @@
     </row>
     <row r="875" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="B875" t="s">
         <v>1500</v>
@@ -13360,7 +13360,7 @@
     </row>
     <row r="877" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="B877" t="s">
         <v>1500</v>
@@ -13392,7 +13392,7 @@
     </row>
     <row r="881" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="B881" t="s">
         <v>1500</v>
@@ -13488,7 +13488,7 @@
     </row>
     <row r="893" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="B893" t="s">
         <v>1500</v>
@@ -13544,7 +13544,7 @@
     </row>
     <row r="900" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="B900" t="s">
         <v>1500</v>
@@ -13552,7 +13552,7 @@
     </row>
     <row r="901" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="B901" t="s">
         <v>1500</v>
@@ -13592,7 +13592,7 @@
     </row>
     <row r="906" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="B906" t="s">
         <v>1500</v>
@@ -13656,7 +13656,7 @@
     </row>
     <row r="914" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="B914" t="s">
         <v>1500</v>
@@ -13672,7 +13672,7 @@
     </row>
     <row r="916" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="B916" t="s">
         <v>1500</v>
@@ -13688,7 +13688,7 @@
     </row>
     <row r="918" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="B918" t="s">
         <v>1500</v>
@@ -13704,7 +13704,7 @@
     </row>
     <row r="920" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="B920" t="s">
         <v>1500</v>
@@ -13752,7 +13752,7 @@
     </row>
     <row r="926" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="B926" t="s">
         <v>1500</v>
@@ -13808,7 +13808,7 @@
     </row>
     <row r="933" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="B933" t="s">
         <v>1500</v>
@@ -13832,7 +13832,7 @@
     </row>
     <row r="936" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="B936" t="s">
         <v>1500</v>
@@ -13864,7 +13864,7 @@
     </row>
     <row r="940" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="B940" t="s">
         <v>1500</v>
@@ -13992,7 +13992,7 @@
     </row>
     <row r="956" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="B956" t="s">
         <v>1500</v>
@@ -14024,7 +14024,7 @@
     </row>
     <row r="960" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="B960" t="s">
         <v>1500</v>
@@ -14184,7 +14184,7 @@
     </row>
     <row r="980" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="B980" t="s">
         <v>1500</v>
@@ -14256,7 +14256,7 @@
     </row>
     <row r="989" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="B989" t="s">
         <v>1500</v>
@@ -14296,7 +14296,7 @@
     </row>
     <row r="994" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="B994" t="s">
         <v>1500</v>
@@ -14312,7 +14312,7 @@
     </row>
     <row r="996" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="B996" t="s">
         <v>1500</v>
@@ -14328,7 +14328,7 @@
     </row>
     <row r="998" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="B998" t="s">
         <v>1500</v>
@@ -14392,7 +14392,7 @@
     </row>
     <row r="1006" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="B1006" t="s">
         <v>1500</v>
@@ -14504,7 +14504,7 @@
     </row>
     <row r="1020" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="B1020" t="s">
         <v>1501</v>
@@ -14560,7 +14560,7 @@
     </row>
     <row r="1027" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="B1027" t="s">
         <v>1501</v>
@@ -14584,7 +14584,7 @@
     </row>
     <row r="1030" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1030" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="B1030" t="s">
         <v>1501</v>
@@ -14600,7 +14600,7 @@
     </row>
     <row r="1032" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="B1032" t="s">
         <v>1501</v>
@@ -14632,7 +14632,7 @@
     </row>
     <row r="1036" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1036" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="B1036" t="s">
         <v>1501</v>
@@ -14752,7 +14752,7 @@
     </row>
     <row r="1051" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1051" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="B1051" t="s">
         <v>1501</v>
@@ -14808,7 +14808,7 @@
     </row>
     <row r="1058" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1058" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="B1058" t="s">
         <v>1501</v>
@@ -14880,7 +14880,7 @@
     </row>
     <row r="1067" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1067" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="B1067" t="s">
         <v>1501</v>
@@ -15048,7 +15048,7 @@
     </row>
     <row r="1088" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1088" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B1088" t="s">
         <v>1501</v>
@@ -15168,7 +15168,7 @@
     </row>
     <row r="1103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1103" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B1103" t="s">
         <v>1501</v>
@@ -15216,7 +15216,7 @@
     </row>
     <row r="1109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1109" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="B1109" t="s">
         <v>1501</v>
@@ -15376,7 +15376,7 @@
     </row>
     <row r="1129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1129" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="B1129" t="s">
         <v>1501</v>
@@ -15464,7 +15464,7 @@
     </row>
     <row r="1140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1140" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="B1140" t="s">
         <v>1501</v>
@@ -15488,7 +15488,7 @@
     </row>
     <row r="1143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1143" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="B1143" t="s">
         <v>1501</v>
@@ -15512,7 +15512,7 @@
     </row>
     <row r="1146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1146" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="B1146" t="s">
         <v>1501</v>
@@ -15536,7 +15536,7 @@
     </row>
     <row r="1149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1149" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="B1149" t="s">
         <v>1501</v>
@@ -15560,7 +15560,7 @@
     </row>
     <row r="1152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1152" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="B1152" t="s">
         <v>1501</v>
@@ -15576,7 +15576,7 @@
     </row>
     <row r="1154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1154" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="B1154" t="s">
         <v>1501</v>
@@ -15592,7 +15592,7 @@
     </row>
     <row r="1156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1156" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="B1156" t="s">
         <v>1501</v>
@@ -15640,7 +15640,7 @@
     </row>
     <row r="1162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1162" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="B1162" t="s">
         <v>1501</v>
@@ -15736,7 +15736,7 @@
     </row>
     <row r="1174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1174" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="B1174" t="s">
         <v>1501</v>
@@ -15824,7 +15824,7 @@
     </row>
     <row r="1185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1185" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="B1185" t="s">
         <v>1501</v>
@@ -15928,7 +15928,7 @@
     </row>
     <row r="1198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1198" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="B1198" t="s">
         <v>1501</v>
@@ -16032,7 +16032,7 @@
     </row>
     <row r="1211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1211" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="B1211" t="s">
         <v>1501</v>
@@ -16056,7 +16056,7 @@
     </row>
     <row r="1214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1214" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="B1214" t="s">
         <v>1501</v>
@@ -16064,7 +16064,7 @@
     </row>
     <row r="1215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1215" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="B1215" t="s">
         <v>1501</v>
@@ -16072,7 +16072,7 @@
     </row>
     <row r="1216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1216" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="B1216" t="s">
         <v>1501</v>
@@ -16080,7 +16080,7 @@
     </row>
     <row r="1217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1217" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="B1217" t="s">
         <v>1501</v>
@@ -16104,7 +16104,7 @@
     </row>
     <row r="1220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1220" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="B1220" t="s">
         <v>1501</v>
@@ -16168,7 +16168,7 @@
     </row>
     <row r="1228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1228" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="B1228" t="s">
         <v>1501</v>
@@ -16192,7 +16192,7 @@
     </row>
     <row r="1231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1231" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="B1231" t="s">
         <v>1501</v>
@@ -16256,7 +16256,7 @@
     </row>
     <row r="1239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1239" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="B1239" t="s">
         <v>1501</v>
@@ -16280,7 +16280,7 @@
     </row>
     <row r="1242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1242" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="B1242" t="s">
         <v>1501</v>
@@ -16368,7 +16368,7 @@
     </row>
     <row r="1253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1253" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="B1253" t="s">
         <v>1501</v>
@@ -16416,7 +16416,7 @@
     </row>
     <row r="1259" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1259" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="B1259" t="s">
         <v>1501</v>
@@ -16504,7 +16504,7 @@
     </row>
     <row r="1270" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1270" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="B1270" t="s">
         <v>1501</v>
@@ -16632,7 +16632,7 @@
     </row>
     <row r="1286" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1286" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="B1286" t="s">
         <v>1502</v>
@@ -16664,7 +16664,7 @@
     </row>
     <row r="1290" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1290" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B1290" t="s">
         <v>1502</v>
@@ -16680,7 +16680,7 @@
     </row>
     <row r="1292" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1292" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="B1292" t="s">
         <v>1502</v>
@@ -16768,7 +16768,7 @@
     </row>
     <row r="1303" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1303" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="B1303" t="s">
         <v>1502</v>
@@ -16784,7 +16784,7 @@
     </row>
     <row r="1305" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1305" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="B1305" t="s">
         <v>1502</v>
@@ -16808,7 +16808,7 @@
     </row>
     <row r="1308" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1308" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="B1308" t="s">
         <v>1502</v>
@@ -16824,7 +16824,7 @@
     </row>
     <row r="1310" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1310" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="B1310" t="s">
         <v>1502</v>
@@ -16840,7 +16840,7 @@
     </row>
     <row r="1312" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1312" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="B1312" t="s">
         <v>1502</v>
@@ -16864,7 +16864,7 @@
     </row>
     <row r="1315" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1315" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="B1315" t="s">
         <v>1502</v>
@@ -16888,7 +16888,7 @@
     </row>
     <row r="1318" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1318" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="B1318" t="s">
         <v>1502</v>
@@ -16904,7 +16904,7 @@
     </row>
     <row r="1320" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1320" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="B1320" t="s">
         <v>1502</v>
@@ -16944,7 +16944,7 @@
     </row>
     <row r="1325" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1325" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="B1325" t="s">
         <v>1502</v>
@@ -17008,7 +17008,7 @@
     </row>
     <row r="1333" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1333" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="B1333" t="s">
         <v>1502</v>
@@ -17024,7 +17024,7 @@
     </row>
     <row r="1335" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1335" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="B1335" t="s">
         <v>1502</v>
@@ -17048,7 +17048,7 @@
     </row>
     <row r="1338" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1338" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="B1338" t="s">
         <v>1502</v>
@@ -17080,7 +17080,7 @@
     </row>
     <row r="1342" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1342" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="B1342" t="s">
         <v>1502</v>
@@ -17088,7 +17088,7 @@
     </row>
     <row r="1343" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1343" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="B1343" t="s">
         <v>1502</v>
@@ -17160,7 +17160,7 @@
     </row>
     <row r="1352" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1352" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="B1352" t="s">
         <v>1502</v>
@@ -17200,7 +17200,7 @@
     </row>
     <row r="1357" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1357" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="B1357" t="s">
         <v>1502</v>
@@ -17240,7 +17240,7 @@
     </row>
     <row r="1362" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1362" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="B1362" t="s">
         <v>1502</v>
@@ -17264,7 +17264,7 @@
     </row>
     <row r="1365" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1365" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="B1365" t="s">
         <v>1502</v>
@@ -17288,7 +17288,7 @@
     </row>
     <row r="1368" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1368" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="B1368" t="s">
         <v>1502</v>
@@ -17328,7 +17328,7 @@
     </row>
     <row r="1373" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1373" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="B1373" t="s">
         <v>1502</v>
@@ -17408,7 +17408,7 @@
     </row>
     <row r="1383" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1383" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="B1383" t="s">
         <v>1502</v>
@@ -17416,7 +17416,7 @@
     </row>
     <row r="1384" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1384" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="B1384" t="s">
         <v>1502</v>
@@ -17488,7 +17488,7 @@
     </row>
     <row r="1393" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1393" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="B1393" t="s">
         <v>1502</v>
@@ -17496,7 +17496,7 @@
     </row>
     <row r="1394" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1394" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="B1394" t="s">
         <v>1502</v>
@@ -17504,7 +17504,7 @@
     </row>
     <row r="1395" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1395" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="B1395" t="s">
         <v>1502</v>
@@ -17528,7 +17528,7 @@
     </row>
     <row r="1398" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1398" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="B1398" t="s">
         <v>1502</v>
@@ -17544,7 +17544,7 @@
     </row>
     <row r="1400" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1400" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="B1400" t="s">
         <v>1502</v>
@@ -17584,7 +17584,7 @@
     </row>
     <row r="1405" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1405" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="B1405" t="s">
         <v>1502</v>
@@ -17600,7 +17600,7 @@
     </row>
     <row r="1407" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1407" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="B1407" t="s">
         <v>1502</v>
@@ -17632,7 +17632,7 @@
     </row>
     <row r="1411" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1411" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="B1411" t="s">
         <v>1502</v>
@@ -17656,7 +17656,7 @@
     </row>
     <row r="1414" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1414" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="B1414" t="s">
         <v>1502</v>
@@ -17688,7 +17688,7 @@
     </row>
     <row r="1418" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1418" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="B1418" t="s">
         <v>1502</v>
@@ -17696,7 +17696,7 @@
     </row>
     <row r="1419" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1419" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="B1419" t="s">
         <v>1502</v>
@@ -17704,7 +17704,7 @@
     </row>
     <row r="1420" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1420" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="B1420" t="s">
         <v>1502</v>
@@ -17728,7 +17728,7 @@
     </row>
     <row r="1423" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1423" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="B1423" t="s">
         <v>1502</v>
@@ -17736,7 +17736,7 @@
     </row>
     <row r="1424" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1424" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="B1424" t="s">
         <v>1502</v>
@@ -17760,7 +17760,7 @@
     </row>
     <row r="1427" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1427" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="B1427" t="s">
         <v>1502</v>
@@ -17784,7 +17784,7 @@
     </row>
     <row r="1430" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1430" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="B1430" t="s">
         <v>1502</v>
@@ -17800,7 +17800,7 @@
     </row>
     <row r="1432" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1432" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="B1432" t="s">
         <v>1502</v>
@@ -17808,7 +17808,7 @@
     </row>
     <row r="1433" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1433" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="B1433" t="s">
         <v>1502</v>
@@ -17824,7 +17824,7 @@
     </row>
     <row r="1435" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1435" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B1435" t="s">
         <v>1502</v>
@@ -17832,7 +17832,7 @@
     </row>
     <row r="1436" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1436" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="B1436" t="s">
         <v>1502</v>
@@ -17848,7 +17848,7 @@
     </row>
     <row r="1438" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1438" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="B1438" t="s">
         <v>1502</v>
@@ -17856,7 +17856,7 @@
     </row>
     <row r="1439" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1439" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="B1439" t="s">
         <v>1502</v>
@@ -17864,7 +17864,7 @@
     </row>
     <row r="1440" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1440" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="B1440" t="s">
         <v>1502</v>
@@ -17888,7 +17888,7 @@
     </row>
     <row r="1443" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1443" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="B1443" t="s">
         <v>1502</v>
@@ -17928,7 +17928,7 @@
     </row>
     <row r="1448" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1448" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="B1448" t="s">
         <v>1502</v>
@@ -17936,7 +17936,7 @@
     </row>
     <row r="1449" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1449" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="B1449" t="s">
         <v>1502</v>
@@ -17952,7 +17952,7 @@
     </row>
     <row r="1451" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1451" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="B1451" t="s">
         <v>1502</v>
@@ -17968,7 +17968,7 @@
     </row>
     <row r="1453" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1453" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="B1453" t="s">
         <v>1502</v>
@@ -17984,7 +17984,7 @@
     </row>
     <row r="1455" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1455" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="B1455" t="s">
         <v>1502</v>
@@ -17992,7 +17992,7 @@
     </row>
     <row r="1456" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1456" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="B1456" t="s">
         <v>1502</v>
@@ -18008,7 +18008,7 @@
     </row>
     <row r="1458" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1458" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="B1458" t="s">
         <v>1502</v>
@@ -18080,7 +18080,7 @@
     </row>
     <row r="1467" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1467" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="B1467" t="s">
         <v>1502</v>
@@ -18104,7 +18104,7 @@
     </row>
     <row r="1470" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1470" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="B1470" t="s">
         <v>1502</v>
@@ -18120,7 +18120,7 @@
     </row>
     <row r="1472" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1472" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="B1472" t="s">
         <v>1502</v>
@@ -18128,7 +18128,7 @@
     </row>
     <row r="1473" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1473" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="B1473" t="s">
         <v>1502</v>
@@ -18136,7 +18136,7 @@
     </row>
     <row r="1474" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1474" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="B1474" t="s">
         <v>1502</v>
@@ -18144,7 +18144,7 @@
     </row>
     <row r="1475" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1475" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="B1475" t="s">
         <v>1502</v>
@@ -18168,7 +18168,7 @@
     </row>
     <row r="1478" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1478" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="B1478" t="s">
         <v>1502</v>
@@ -18176,7 +18176,7 @@
     </row>
     <row r="1479" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1479" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="B1479" t="s">
         <v>1502</v>
@@ -18184,7 +18184,7 @@
     </row>
     <row r="1480" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1480" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="B1480" t="s">
         <v>1502</v>
@@ -18200,7 +18200,7 @@
     </row>
     <row r="1482" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1482" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="B1482" t="s">
         <v>1502</v>
@@ -18240,7 +18240,7 @@
     </row>
     <row r="1487" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1487" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="B1487" t="s">
         <v>1502</v>
@@ -18280,7 +18280,7 @@
     </row>
     <row r="1492" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1492" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="B1492" t="s">
         <v>1502</v>
@@ -18320,7 +18320,7 @@
     </row>
     <row r="1497" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1497" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="B1497" t="s">
         <v>1502</v>
@@ -18328,7 +18328,7 @@
     </row>
     <row r="1498" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1498" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="B1498" t="s">
         <v>1502</v>
@@ -18376,7 +18376,7 @@
     </row>
     <row r="1504" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1504" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="B1504" t="s">
         <v>1502</v>
@@ -18384,7 +18384,7 @@
     </row>
     <row r="1505" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1505" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="B1505" t="s">
         <v>1502</v>
@@ -18392,7 +18392,7 @@
     </row>
     <row r="1506" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1506" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="B1506" t="s">
         <v>1502</v>
@@ -18408,7 +18408,7 @@
     </row>
     <row r="1508" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1508" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="B1508" t="s">
         <v>1502</v>
@@ -18448,7 +18448,7 @@
     </row>
     <row r="1513" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1513" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="B1513" t="s">
         <v>1502</v>
@@ -18456,7 +18456,7 @@
     </row>
     <row r="1514" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1514" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="B1514" t="s">
         <v>1502</v>
@@ -18464,7 +18464,7 @@
     </row>
     <row r="1515" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1515" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="B1515" t="s">
         <v>1502</v>
@@ -18488,7 +18488,7 @@
     </row>
     <row r="1518" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1518" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="B1518" t="s">
         <v>1502</v>
@@ -18504,7 +18504,7 @@
     </row>
     <row r="1520" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1520" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="B1520" t="s">
         <v>1502</v>
@@ -18512,7 +18512,7 @@
     </row>
     <row r="1521" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1521" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="B1521" t="s">
         <v>1502</v>
@@ -18536,7 +18536,7 @@
     </row>
     <row r="1524" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1524" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="B1524" t="s">
         <v>1502</v>
@@ -18544,7 +18544,7 @@
     </row>
     <row r="1525" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1525" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="B1525" t="s">
         <v>1502</v>
@@ -18552,7 +18552,7 @@
     </row>
     <row r="1526" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1526" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="B1526" t="s">
         <v>1502</v>
@@ -18584,7 +18584,7 @@
     </row>
     <row r="1530" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1530" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="B1530" t="s">
         <v>1502</v>
@@ -18592,7 +18592,7 @@
     </row>
     <row r="1531" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1531" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="B1531" t="s">
         <v>1502</v>
@@ -18600,7 +18600,7 @@
     </row>
     <row r="1532" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1532" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="B1532" t="s">
         <v>1502</v>
@@ -18616,7 +18616,7 @@
     </row>
     <row r="1534" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1534" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="B1534" t="s">
         <v>1502</v>
@@ -18632,7 +18632,7 @@
     </row>
     <row r="1536" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1536" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="B1536" t="s">
         <v>1502</v>
@@ -18656,7 +18656,7 @@
     </row>
     <row r="1539" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1539" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="B1539" t="s">
         <v>1502</v>
@@ -18672,7 +18672,7 @@
     </row>
     <row r="1541" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1541" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="B1541" t="s">
         <v>1502</v>
@@ -18680,7 +18680,7 @@
     </row>
     <row r="1542" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1542" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="B1542" t="s">
         <v>1502</v>
@@ -18688,7 +18688,7 @@
     </row>
     <row r="1543" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1543" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="B1543" t="s">
         <v>1502</v>
@@ -18696,7 +18696,7 @@
     </row>
     <row r="1544" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1544" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B1544" t="s">
         <v>1502</v>
@@ -18712,7 +18712,7 @@
     </row>
     <row r="1546" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1546" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="B1546" t="s">
         <v>1502</v>
@@ -18728,7 +18728,7 @@
     </row>
     <row r="1548" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1548" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="B1548" t="s">
         <v>1502</v>
@@ -18744,7 +18744,7 @@
     </row>
     <row r="1550" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1550" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="B1550" t="s">
         <v>1502</v>
@@ -18752,7 +18752,7 @@
     </row>
     <row r="1551" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1551" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="B1551" t="s">
         <v>1502</v>
@@ -18768,7 +18768,7 @@
     </row>
     <row r="1553" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1553" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="B1553" t="s">
         <v>1502</v>
@@ -18784,7 +18784,7 @@
     </row>
     <row r="1555" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1555" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="B1555" t="s">
         <v>1502</v>
@@ -18792,7 +18792,7 @@
     </row>
     <row r="1556" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1556" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="B1556" t="s">
         <v>1502</v>
@@ -18824,7 +18824,7 @@
     </row>
     <row r="1560" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1560" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="B1560" t="s">
         <v>1502</v>
@@ -18832,7 +18832,7 @@
     </row>
     <row r="1561" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1561" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="B1561" t="s">
         <v>1502</v>
@@ -18840,7 +18840,7 @@
     </row>
     <row r="1562" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1562" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="B1562" t="s">
         <v>1502</v>
@@ -18848,7 +18848,7 @@
     </row>
     <row r="1563" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1563" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="B1563" t="s">
         <v>1502</v>
@@ -18864,7 +18864,7 @@
     </row>
     <row r="1565" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1565" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="B1565" t="s">
         <v>1502</v>
@@ -18888,7 +18888,7 @@
     </row>
     <row r="1568" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1568" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="B1568" t="s">
         <v>1502</v>
@@ -18896,7 +18896,7 @@
     </row>
     <row r="1569" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1569" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="B1569" t="s">
         <v>1502</v>
@@ -18904,7 +18904,7 @@
     </row>
     <row r="1570" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1570" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="B1570" t="s">
         <v>1502</v>
@@ -18920,7 +18920,7 @@
     </row>
     <row r="1572" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1572" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="B1572" t="s">
         <v>1502</v>
@@ -18944,7 +18944,7 @@
     </row>
     <row r="1575" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1575" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="B1575" t="s">
         <v>1502</v>
@@ -18952,7 +18952,7 @@
     </row>
     <row r="1576" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1576" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="B1576" t="s">
         <v>1502</v>
@@ -18960,7 +18960,7 @@
     </row>
     <row r="1577" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1577" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="B1577" t="s">
         <v>1502</v>
@@ -18968,7 +18968,7 @@
     </row>
     <row r="1578" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1578" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="B1578" t="s">
         <v>1502</v>
@@ -19000,7 +19000,7 @@
     </row>
     <row r="1582" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1582" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="B1582" t="s">
         <v>1502</v>
@@ -19008,7 +19008,7 @@
     </row>
     <row r="1583" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1583" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="B1583" t="s">
         <v>1502</v>
@@ -19016,7 +19016,7 @@
     </row>
     <row r="1584" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1584" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="B1584" t="s">
         <v>1502</v>
@@ -19024,7 +19024,7 @@
     </row>
     <row r="1585" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1585" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="B1585" t="s">
         <v>1502</v>
@@ -19040,7 +19040,7 @@
     </row>
     <row r="1587" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1587" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="B1587" t="s">
         <v>1502</v>
@@ -19048,7 +19048,7 @@
     </row>
     <row r="1588" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1588" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="B1588" t="s">
         <v>1502</v>
@@ -19056,7 +19056,7 @@
     </row>
     <row r="1589" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1589" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="B1589" t="s">
         <v>1502</v>
@@ -19072,7 +19072,7 @@
     </row>
     <row r="1591" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1591" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="B1591" t="s">
         <v>1502</v>
@@ -19080,7 +19080,7 @@
     </row>
     <row r="1592" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1592" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="B1592" t="s">
         <v>1502</v>
@@ -19096,7 +19096,7 @@
     </row>
     <row r="1594" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1594" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="B1594" t="s">
         <v>1502</v>
@@ -19112,7 +19112,7 @@
     </row>
     <row r="1596" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1596" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="B1596" t="s">
         <v>1502</v>
@@ -19128,7 +19128,7 @@
     </row>
     <row r="1598" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1598" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="B1598" t="s">
         <v>1502</v>
@@ -19136,7 +19136,7 @@
     </row>
     <row r="1599" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1599" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="B1599" t="s">
         <v>1502</v>
@@ -19160,7 +19160,7 @@
     </row>
     <row r="1602" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1602" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="B1602" t="s">
         <v>1502</v>
@@ -19176,7 +19176,7 @@
     </row>
     <row r="1604" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1604" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="B1604" t="s">
         <v>1502</v>
@@ -19200,7 +19200,7 @@
     </row>
     <row r="1607" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1607" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="B1607" t="s">
         <v>1502</v>
@@ -19208,7 +19208,7 @@
     </row>
     <row r="1608" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1608" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="B1608" t="s">
         <v>1502</v>
@@ -19232,7 +19232,7 @@
     </row>
     <row r="1611" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1611" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="B1611" t="s">
         <v>1502</v>
@@ -19240,7 +19240,7 @@
     </row>
     <row r="1612" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1612" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="B1612" t="s">
         <v>1502</v>
@@ -19248,7 +19248,7 @@
     </row>
     <row r="1613" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1613" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="B1613" t="s">
         <v>1502</v>
@@ -19264,7 +19264,7 @@
     </row>
     <row r="1615" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1615" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="B1615" t="s">
         <v>1502</v>
@@ -19272,7 +19272,7 @@
     </row>
     <row r="1616" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1616" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="B1616" t="s">
         <v>1502</v>
@@ -19280,7 +19280,7 @@
     </row>
     <row r="1617" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1617" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="B1617" t="s">
         <v>1502</v>
@@ -19288,7 +19288,7 @@
     </row>
     <row r="1618" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1618" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="B1618" t="s">
         <v>1502</v>
@@ -19296,7 +19296,7 @@
     </row>
     <row r="1619" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1619" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B1619" t="s">
         <v>1502</v>
@@ -19312,7 +19312,7 @@
     </row>
     <row r="1621" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1621" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="B1621" t="s">
         <v>1502</v>
@@ -19320,7 +19320,7 @@
     </row>
     <row r="1622" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1622" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="B1622" t="s">
         <v>1502</v>
@@ -19328,7 +19328,7 @@
     </row>
     <row r="1623" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1623" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="B1623" t="s">
         <v>1502</v>
@@ -19336,7 +19336,7 @@
     </row>
     <row r="1624" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1624" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="B1624" t="s">
         <v>1502</v>
@@ -19344,7 +19344,7 @@
     </row>
     <row r="1625" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1625" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="B1625" t="s">
         <v>1502</v>
@@ -19352,7 +19352,7 @@
     </row>
     <row r="1626" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1626" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="B1626" t="s">
         <v>1502</v>
@@ -19360,7 +19360,7 @@
     </row>
     <row r="1627" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1627" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="B1627" t="s">
         <v>1502</v>
@@ -19368,7 +19368,7 @@
     </row>
     <row r="1628" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1628" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="B1628" t="s">
         <v>1502</v>
@@ -19376,7 +19376,7 @@
     </row>
     <row r="1629" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1629" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="B1629" t="s">
         <v>1502</v>
@@ -19392,7 +19392,7 @@
     </row>
     <row r="1631" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1631" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="B1631" t="s">
         <v>1502</v>
@@ -19400,7 +19400,7 @@
     </row>
     <row r="1632" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1632" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="B1632" t="s">
         <v>1502</v>
@@ -19408,7 +19408,7 @@
     </row>
     <row r="1633" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1633" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="B1633" t="s">
         <v>1502</v>
@@ -19416,7 +19416,7 @@
     </row>
     <row r="1634" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1634" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="B1634" t="s">
         <v>1502</v>
@@ -19424,7 +19424,7 @@
     </row>
     <row r="1635" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1635" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="B1635" t="s">
         <v>1502</v>
@@ -19432,7 +19432,7 @@
     </row>
     <row r="1636" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1636" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="B1636" t="s">
         <v>1502</v>
@@ -19448,7 +19448,7 @@
     </row>
     <row r="1638" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1638" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="B1638" t="s">
         <v>1502</v>
@@ -19456,7 +19456,7 @@
     </row>
     <row r="1639" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1639" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="B1639" t="s">
         <v>1502</v>
@@ -19464,7 +19464,7 @@
     </row>
     <row r="1640" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1640" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="B1640" t="s">
         <v>1502</v>
@@ -19472,7 +19472,7 @@
     </row>
     <row r="1641" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1641" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="B1641" t="s">
         <v>1502</v>
@@ -19488,7 +19488,7 @@
     </row>
     <row r="1643" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1643" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="B1643" t="s">
         <v>1502</v>
@@ -19504,7 +19504,7 @@
     </row>
     <row r="1645" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1645" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="B1645" t="s">
         <v>1502</v>
@@ -19512,7 +19512,7 @@
     </row>
     <row r="1646" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1646" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="B1646" t="s">
         <v>1502</v>
@@ -19520,7 +19520,7 @@
     </row>
     <row r="1647" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1647" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="B1647" t="s">
         <v>1502</v>
@@ -19528,7 +19528,7 @@
     </row>
     <row r="1648" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1648" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="B1648" t="s">
         <v>1502</v>
@@ -19536,7 +19536,7 @@
     </row>
     <row r="1649" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1649" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="B1649" t="s">
         <v>1502</v>
@@ -19544,7 +19544,7 @@
     </row>
     <row r="1650" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1650" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="B1650" t="s">
         <v>1502</v>
@@ -19552,7 +19552,7 @@
     </row>
     <row r="1651" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1651" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="B1651" t="s">
         <v>1502</v>
@@ -19560,7 +19560,7 @@
     </row>
     <row r="1652" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1652" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="B1652" t="s">
         <v>1502</v>
@@ -19568,7 +19568,7 @@
     </row>
     <row r="1653" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1653" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="B1653" t="s">
         <v>1502</v>
@@ -19584,7 +19584,7 @@
     </row>
     <row r="1655" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1655" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="B1655" t="s">
         <v>1502</v>
@@ -19592,7 +19592,7 @@
     </row>
     <row r="1656" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1656" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="B1656" t="s">
         <v>1502</v>
@@ -19600,7 +19600,7 @@
     </row>
     <row r="1657" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1657" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="B1657" t="s">
         <v>1502</v>
@@ -19616,7 +19616,7 @@
     </row>
     <row r="1659" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1659" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="B1659" t="s">
         <v>1502</v>
@@ -19624,7 +19624,7 @@
     </row>
     <row r="1660" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1660" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="B1660" t="s">
         <v>1502</v>
@@ -19632,7 +19632,7 @@
     </row>
     <row r="1661" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1661" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="B1661" t="s">
         <v>1502</v>
@@ -19640,7 +19640,7 @@
     </row>
     <row r="1662" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1662" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="B1662" t="s">
         <v>1502</v>
@@ -19656,7 +19656,7 @@
     </row>
     <row r="1664" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1664" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="B1664" t="s">
         <v>1502</v>
@@ -19664,7 +19664,7 @@
     </row>
     <row r="1665" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1665" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="B1665" t="s">
         <v>1502</v>
@@ -19672,7 +19672,7 @@
     </row>
     <row r="1666" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1666" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="B1666" t="s">
         <v>1502</v>
@@ -19680,7 +19680,7 @@
     </row>
     <row r="1667" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1667" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="B1667" t="s">
         <v>1502</v>
@@ -19688,7 +19688,7 @@
     </row>
     <row r="1668" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1668" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="B1668" t="s">
         <v>1502</v>
@@ -19696,7 +19696,7 @@
     </row>
     <row r="1669" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1669" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="B1669" t="s">
         <v>1502</v>
@@ -19704,7 +19704,7 @@
     </row>
     <row r="1670" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1670" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="B1670" t="s">
         <v>1502</v>
@@ -19720,7 +19720,7 @@
     </row>
     <row r="1672" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1672" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="B1672" t="s">
         <v>1502</v>
@@ -19728,7 +19728,7 @@
     </row>
     <row r="1673" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1673" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="B1673" t="s">
         <v>1502</v>
@@ -19736,7 +19736,7 @@
     </row>
     <row r="1674" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1674" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="B1674" t="s">
         <v>1502</v>
@@ -19744,7 +19744,7 @@
     </row>
     <row r="1675" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1675" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="B1675" t="s">
         <v>1502</v>
@@ -19752,7 +19752,7 @@
     </row>
     <row r="1676" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1676" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="B1676" t="s">
         <v>1502</v>
@@ -19760,7 +19760,7 @@
     </row>
     <row r="1677" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1677" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="B1677" t="s">
         <v>1502</v>
@@ -19768,7 +19768,7 @@
     </row>
     <row r="1678" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1678" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="B1678" t="s">
         <v>1502</v>
@@ -19776,7 +19776,7 @@
     </row>
     <row r="1679" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1679" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="B1679" t="s">
         <v>1502</v>
@@ -19784,7 +19784,7 @@
     </row>
     <row r="1680" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1680" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="B1680" t="s">
         <v>1502</v>
@@ -19792,7 +19792,7 @@
     </row>
     <row r="1681" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1681" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="B1681" t="s">
         <v>1502</v>
@@ -19800,7 +19800,7 @@
     </row>
     <row r="1682" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1682" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="B1682" t="s">
         <v>1502</v>
@@ -19808,7 +19808,7 @@
     </row>
     <row r="1683" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1683" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="B1683" t="s">
         <v>1502</v>
@@ -19816,7 +19816,7 @@
     </row>
     <row r="1684" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1684" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="B1684" t="s">
         <v>1502</v>
@@ -19824,7 +19824,7 @@
     </row>
     <row r="1685" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1685" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="B1685" t="s">
         <v>1502</v>
@@ -19832,7 +19832,7 @@
     </row>
     <row r="1686" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1686" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="B1686" t="s">
         <v>1502</v>
@@ -19840,7 +19840,7 @@
     </row>
     <row r="1687" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1687" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="B1687" t="s">
         <v>1502</v>
@@ -19848,7 +19848,7 @@
     </row>
     <row r="1688" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1688" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="B1688" t="s">
         <v>1502</v>
@@ -19856,7 +19856,7 @@
     </row>
     <row r="1689" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1689" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="B1689" t="s">
         <v>1502</v>
@@ -19864,7 +19864,7 @@
     </row>
     <row r="1690" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1690" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="B1690" t="s">
         <v>1502</v>
@@ -19872,7 +19872,7 @@
     </row>
     <row r="1691" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1691" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="B1691" t="s">
         <v>1502</v>
@@ -19880,7 +19880,7 @@
     </row>
     <row r="1692" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1692" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="B1692" t="s">
         <v>1502</v>
@@ -19896,7 +19896,7 @@
     </row>
     <row r="1694" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1694" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="B1694" t="s">
         <v>1502</v>
@@ -19904,7 +19904,7 @@
     </row>
     <row r="1695" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1695" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="B1695" t="s">
         <v>1502</v>
@@ -19912,7 +19912,7 @@
     </row>
     <row r="1696" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1696" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="B1696" t="s">
         <v>1502</v>
@@ -19920,7 +19920,7 @@
     </row>
     <row r="1697" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1697" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="B1697" t="s">
         <v>1502</v>
@@ -19928,7 +19928,7 @@
     </row>
     <row r="1698" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1698" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="B1698" t="s">
         <v>1502</v>
@@ -19936,7 +19936,7 @@
     </row>
     <row r="1699" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1699" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="B1699" t="s">
         <v>1502</v>
@@ -19944,7 +19944,7 @@
     </row>
     <row r="1700" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1700" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="B1700" t="s">
         <v>1502</v>
@@ -19952,7 +19952,7 @@
     </row>
     <row r="1701" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1701" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="B1701" t="s">
         <v>1502</v>
@@ -19968,7 +19968,7 @@
     </row>
     <row r="1703" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1703" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="B1703" t="s">
         <v>1502</v>
@@ -19976,7 +19976,7 @@
     </row>
     <row r="1704" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1704" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="B1704" t="s">
         <v>1502</v>
@@ -19984,7 +19984,7 @@
     </row>
     <row r="1705" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1705" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="B1705" t="s">
         <v>1502</v>
@@ -20008,7 +20008,7 @@
     </row>
     <row r="1708" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1708" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="B1708" t="s">
         <v>1502</v>
@@ -20016,7 +20016,7 @@
     </row>
     <row r="1709" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1709" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="B1709" t="s">
         <v>1502</v>
@@ -20024,7 +20024,7 @@
     </row>
     <row r="1710" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1710" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="B1710" t="s">
         <v>1502</v>
@@ -20032,7 +20032,7 @@
     </row>
     <row r="1711" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1711" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="B1711" t="s">
         <v>1502</v>
@@ -20040,7 +20040,7 @@
     </row>
     <row r="1712" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1712" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="B1712" t="s">
         <v>1502</v>
@@ -20048,7 +20048,7 @@
     </row>
     <row r="1713" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1713" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="B1713" t="s">
         <v>1502</v>
@@ -20056,7 +20056,7 @@
     </row>
     <row r="1714" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1714" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="B1714" t="s">
         <v>1502</v>
@@ -20064,7 +20064,7 @@
     </row>
     <row r="1715" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1715" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="B1715" t="s">
         <v>1502</v>
@@ -20072,7 +20072,7 @@
     </row>
     <row r="1716" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1716" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="B1716" t="s">
         <v>1502</v>
@@ -20080,7 +20080,7 @@
     </row>
     <row r="1717" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1717" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="B1717" t="s">
         <v>1502</v>
@@ -20088,7 +20088,7 @@
     </row>
     <row r="1718" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1718" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="B1718" t="s">
         <v>1502</v>
@@ -20104,7 +20104,7 @@
     </row>
     <row r="1720" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1720" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="B1720" t="s">
         <v>1502</v>
@@ -20112,7 +20112,7 @@
     </row>
     <row r="1721" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1721" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="B1721" t="s">
         <v>1502</v>
@@ -20128,7 +20128,7 @@
     </row>
     <row r="1723" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1723" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="B1723" t="s">
         <v>1502</v>
@@ -20136,7 +20136,7 @@
     </row>
     <row r="1724" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1724" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="B1724" t="s">
         <v>1502</v>
@@ -20144,7 +20144,7 @@
     </row>
     <row r="1725" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1725" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="B1725" t="s">
         <v>1502</v>
@@ -20152,7 +20152,7 @@
     </row>
     <row r="1726" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1726" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="B1726" t="s">
         <v>1502</v>
@@ -20160,7 +20160,7 @@
     </row>
     <row r="1727" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1727" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="B1727" t="s">
         <v>1502</v>
@@ -20168,7 +20168,7 @@
     </row>
     <row r="1728" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1728" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="B1728" t="s">
         <v>1502</v>
@@ -20176,7 +20176,7 @@
     </row>
     <row r="1729" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1729" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="B1729" t="s">
         <v>1502</v>
@@ -20184,7 +20184,7 @@
     </row>
     <row r="1730" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1730" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="B1730" t="s">
         <v>1502</v>
@@ -20192,7 +20192,7 @@
     </row>
     <row r="1731" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1731" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="B1731" t="s">
         <v>1502</v>
@@ -20200,7 +20200,7 @@
     </row>
     <row r="1732" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1732" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="B1732" t="s">
         <v>1502</v>
@@ -20208,7 +20208,7 @@
     </row>
     <row r="1733" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1733" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="B1733" t="s">
         <v>1502</v>
@@ -20224,7 +20224,7 @@
     </row>
     <row r="1735" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1735" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="B1735" t="s">
         <v>1502</v>
@@ -20232,7 +20232,7 @@
     </row>
     <row r="1736" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1736" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="B1736" t="s">
         <v>1502</v>
@@ -20240,7 +20240,7 @@
     </row>
     <row r="1737" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1737" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="B1737" t="s">
         <v>1502</v>
@@ -20248,7 +20248,7 @@
     </row>
     <row r="1738" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1738" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="B1738" t="s">
         <v>1502</v>
@@ -20256,7 +20256,7 @@
     </row>
     <row r="1739" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1739" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="B1739" t="s">
         <v>1502</v>
@@ -20264,7 +20264,7 @@
     </row>
     <row r="1740" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1740" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="B1740" t="s">
         <v>1502</v>
@@ -20272,7 +20272,7 @@
     </row>
     <row r="1741" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1741" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="B1741" t="s">
         <v>1502</v>
@@ -20280,7 +20280,7 @@
     </row>
     <row r="1742" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1742" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="B1742" t="s">
         <v>1502</v>
@@ -20288,7 +20288,7 @@
     </row>
     <row r="1743" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1743" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="B1743" t="s">
         <v>1502</v>
@@ -20296,7 +20296,7 @@
     </row>
     <row r="1744" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1744" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="B1744" t="s">
         <v>1502</v>
@@ -20304,7 +20304,7 @@
     </row>
     <row r="1745" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1745" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="B1745" t="s">
         <v>1502</v>
@@ -20312,7 +20312,7 @@
     </row>
     <row r="1746" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1746" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="B1746" t="s">
         <v>1502</v>
@@ -20320,7 +20320,7 @@
     </row>
     <row r="1747" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1747" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="B1747" t="s">
         <v>1502</v>
@@ -20328,7 +20328,7 @@
     </row>
     <row r="1748" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1748" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="B1748" t="s">
         <v>1502</v>
@@ -20336,7 +20336,7 @@
     </row>
     <row r="1749" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1749" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="B1749" t="s">
         <v>1502</v>
@@ -20344,7 +20344,7 @@
     </row>
     <row r="1750" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1750" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="B1750" t="s">
         <v>1502</v>
@@ -20352,7 +20352,7 @@
     </row>
     <row r="1751" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1751" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="B1751" t="s">
         <v>1502</v>
@@ -20360,7 +20360,7 @@
     </row>
     <row r="1752" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1752" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="B1752" t="s">
         <v>1502</v>
@@ -20368,7 +20368,7 @@
     </row>
     <row r="1753" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1753" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="B1753" t="s">
         <v>1502</v>
@@ -20384,7 +20384,7 @@
     </row>
     <row r="1755" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1755" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="B1755" t="s">
         <v>1502</v>
@@ -20392,7 +20392,7 @@
     </row>
     <row r="1756" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1756" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="B1756" t="s">
         <v>1502</v>
@@ -20400,7 +20400,7 @@
     </row>
     <row r="1757" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1757" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="B1757" t="s">
         <v>1502</v>
@@ -20408,7 +20408,7 @@
     </row>
     <row r="1758" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1758" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="B1758" t="s">
         <v>1502</v>
@@ -20416,7 +20416,7 @@
     </row>
     <row r="1759" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1759" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="B1759" t="s">
         <v>1502</v>
@@ -20424,7 +20424,7 @@
     </row>
     <row r="1760" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1760" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="B1760" t="s">
         <v>1502</v>
@@ -20440,7 +20440,7 @@
     </row>
     <row r="1762" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1762" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="B1762" t="s">
         <v>1502</v>
@@ -20448,7 +20448,7 @@
     </row>
     <row r="1763" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1763" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="B1763" t="s">
         <v>1502</v>
@@ -20456,7 +20456,7 @@
     </row>
     <row r="1764" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1764" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="B1764" t="s">
         <v>1502</v>
@@ -20464,7 +20464,7 @@
     </row>
     <row r="1765" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1765" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="B1765" t="s">
         <v>1502</v>
@@ -20472,7 +20472,7 @@
     </row>
     <row r="1766" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1766" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="B1766" t="s">
         <v>1502</v>
@@ -20480,7 +20480,7 @@
     </row>
     <row r="1767" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1767" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="B1767" t="s">
         <v>1502</v>
@@ -20488,7 +20488,7 @@
     </row>
     <row r="1768" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1768" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="B1768" t="s">
         <v>1502</v>
@@ -20496,7 +20496,7 @@
     </row>
     <row r="1769" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1769" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="B1769" t="s">
         <v>1502</v>
@@ -20504,7 +20504,7 @@
     </row>
     <row r="1770" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1770" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="B1770" t="s">
         <v>1502</v>
@@ -20520,7 +20520,7 @@
     </row>
     <row r="1772" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1772" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="B1772" t="s">
         <v>1502</v>
@@ -20528,7 +20528,7 @@
     </row>
     <row r="1773" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1773" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="B1773" t="s">
         <v>1502</v>
@@ -20536,7 +20536,7 @@
     </row>
     <row r="1774" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1774" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="B1774" t="s">
         <v>1502</v>
@@ -20544,7 +20544,7 @@
     </row>
     <row r="1775" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1775" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="B1775" t="s">
         <v>1502</v>
@@ -20552,7 +20552,7 @@
     </row>
     <row r="1776" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1776" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="B1776" t="s">
         <v>1502</v>
@@ -20560,7 +20560,7 @@
     </row>
     <row r="1777" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1777" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="B1777" t="s">
         <v>1502</v>
@@ -20568,7 +20568,7 @@
     </row>
     <row r="1778" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1778" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="B1778" t="s">
         <v>1502</v>
@@ -20576,7 +20576,7 @@
     </row>
     <row r="1779" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1779" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="B1779" t="s">
         <v>1502</v>
@@ -20584,7 +20584,7 @@
     </row>
     <row r="1780" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1780" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="B1780" t="s">
         <v>1502</v>
@@ -20592,7 +20592,7 @@
     </row>
     <row r="1781" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1781" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="B1781" t="s">
         <v>1502</v>
@@ -20608,7 +20608,7 @@
     </row>
     <row r="1783" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1783" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="B1783" t="s">
         <v>1502</v>
@@ -20616,7 +20616,7 @@
     </row>
     <row r="1784" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1784" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="B1784" t="s">
         <v>1502</v>
@@ -20632,7 +20632,7 @@
     </row>
     <row r="1786" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1786" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="B1786" t="s">
         <v>1503</v>
@@ -20640,7 +20640,7 @@
     </row>
     <row r="1787" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1787" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="B1787" t="s">
         <v>1503</v>
@@ -20648,7 +20648,7 @@
     </row>
     <row r="1788" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1788" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="B1788" t="s">
         <v>1503</v>
@@ -20656,7 +20656,7 @@
     </row>
     <row r="1789" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1789" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="B1789" t="s">
         <v>1503</v>
@@ -20664,7 +20664,7 @@
     </row>
     <row r="1790" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1790" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="B1790" t="s">
         <v>1503</v>
@@ -20672,7 +20672,7 @@
     </row>
     <row r="1791" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1791" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="B1791" t="s">
         <v>1503</v>
@@ -20680,7 +20680,7 @@
     </row>
     <row r="1792" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1792" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="B1792" t="s">
         <v>1503</v>
@@ -20688,7 +20688,7 @@
     </row>
     <row r="1793" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1793" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="B1793" t="s">
         <v>1503</v>
@@ -20696,7 +20696,7 @@
     </row>
     <row r="1794" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1794" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="B1794" t="s">
         <v>1503</v>
@@ -20704,7 +20704,7 @@
     </row>
     <row r="1795" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1795" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="B1795" t="s">
         <v>1503</v>
@@ -20712,7 +20712,7 @@
     </row>
     <row r="1796" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1796" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="B1796" t="s">
         <v>1503</v>
@@ -20720,7 +20720,7 @@
     </row>
     <row r="1797" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1797" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="B1797" t="s">
         <v>1503</v>
@@ -20728,7 +20728,7 @@
     </row>
     <row r="1798" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1798" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="B1798" t="s">
         <v>1503</v>
@@ -20736,7 +20736,7 @@
     </row>
     <row r="1799" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1799" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="B1799" t="s">
         <v>1503</v>
@@ -20744,7 +20744,7 @@
     </row>
     <row r="1800" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1800" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="B1800" t="s">
         <v>1503</v>
@@ -20752,7 +20752,7 @@
     </row>
     <row r="1801" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1801" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="B1801" t="s">
         <v>1503</v>
@@ -20760,7 +20760,7 @@
     </row>
     <row r="1802" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1802" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="B1802" t="s">
         <v>1503</v>
@@ -20768,7 +20768,7 @@
     </row>
     <row r="1803" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1803" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="B1803" t="s">
         <v>1503</v>
@@ -20776,7 +20776,7 @@
     </row>
     <row r="1804" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1804" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="B1804" t="s">
         <v>1503</v>
@@ -20784,7 +20784,7 @@
     </row>
     <row r="1805" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1805" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="B1805" t="s">
         <v>1503</v>
@@ -21032,7 +21032,7 @@
     </row>
     <row r="1836" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1836" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="B1836" t="s">
         <v>1503</v>
@@ -21040,7 +21040,7 @@
     </row>
     <row r="1837" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1837" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="B1837" t="s">
         <v>1503</v>
@@ -21048,7 +21048,7 @@
     </row>
     <row r="1838" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1838" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="B1838" t="s">
         <v>1503</v>
@@ -21056,7 +21056,7 @@
     </row>
     <row r="1839" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1839" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="B1839" t="s">
         <v>1503</v>
@@ -21064,7 +21064,7 @@
     </row>
     <row r="1840" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1840" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="B1840" t="s">
         <v>1503</v>
@@ -21072,7 +21072,7 @@
     </row>
     <row r="1841" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1841" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="B1841" t="s">
         <v>1503</v>
@@ -21080,7 +21080,7 @@
     </row>
     <row r="1842" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1842" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="B1842" t="s">
         <v>1503</v>
@@ -21088,7 +21088,7 @@
     </row>
     <row r="1843" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1843" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="B1843" t="s">
         <v>1503</v>
@@ -21096,7 +21096,7 @@
     </row>
     <row r="1844" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1844" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="B1844" t="s">
         <v>1503</v>
@@ -21104,7 +21104,7 @@
     </row>
     <row r="1845" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1845" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="B1845" t="s">
         <v>1503</v>
@@ -21112,7 +21112,7 @@
     </row>
     <row r="1846" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1846" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="B1846" t="s">
         <v>1503</v>
@@ -21120,7 +21120,7 @@
     </row>
     <row r="1847" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1847" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="B1847" t="s">
         <v>1503</v>
@@ -21144,7 +21144,7 @@
     </row>
     <row r="1850" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1850" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="B1850" t="s">
         <v>1503</v>
@@ -21376,7 +21376,7 @@
     </row>
     <row r="1879" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1879" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="B1879" t="s">
         <v>1503</v>
@@ -21432,7 +21432,7 @@
     </row>
     <row r="1886" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1886" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="B1886" t="s">
         <v>1503</v>
@@ -21440,7 +21440,7 @@
     </row>
     <row r="1887" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1887" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B1887" t="s">
         <v>1503</v>
@@ -21448,7 +21448,7 @@
     </row>
     <row r="1888" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1888" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="B1888" t="s">
         <v>1503</v>
@@ -22064,7 +22064,7 @@
     </row>
     <row r="1965" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1965" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="B1965" t="s">
         <v>1503</v>
@@ -22072,7 +22072,7 @@
     </row>
     <row r="1966" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1966" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="B1966" t="s">
         <v>1503</v>
@@ -22080,7 +22080,7 @@
     </row>
     <row r="1967" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1967" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="B1967" t="s">
         <v>1503</v>
@@ -22088,7 +22088,7 @@
     </row>
     <row r="1968" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1968" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="B1968" t="s">
         <v>1503</v>
@@ -22096,7 +22096,7 @@
     </row>
     <row r="1969" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1969" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="B1969" t="s">
         <v>1503</v>
@@ -22104,7 +22104,7 @@
     </row>
     <row r="1970" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1970" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="B1970" t="s">
         <v>1503</v>
@@ -22112,7 +22112,7 @@
     </row>
     <row r="1971" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1971" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="B1971" t="s">
         <v>1503</v>
@@ -22120,7 +22120,7 @@
     </row>
     <row r="1972" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1972" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="B1972" t="s">
         <v>1503</v>
